--- a/Beacon Superday-Submission/output/Vendor_Readout.xlsx
+++ b/Beacon Superday-Submission/output/Vendor_Readout.xlsx
@@ -442,16 +442,16 @@
     <t>2025-12-10</t>
   </si>
   <si>
+    <t>PO-4500050024</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
     <t>PO-4500050025</t>
   </si>
   <si>
     <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>PO-4500050024</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
   </si>
   <si>
     <t>PO-4500046863</t>
@@ -5363,7 +5363,7 @@
         <v>139</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K13" t="s">
         <v>106</v>
@@ -5398,7 +5398,7 @@
         <v>141</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14" t="s">
         <v>106</v>
@@ -6979,10 +6979,10 @@
         <v>4600</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H4" t="s">
         <v>251</v>

--- a/Beacon Superday-Submission/output/Vendor_Readout.xlsx
+++ b/Beacon Superday-Submission/output/Vendor_Readout.xlsx
@@ -3443,31 +3443,31 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(B2:B10)</f>
-        <v>0</v>
+        <v>23978261.68</v>
       </c>
       <c r="C11" s="5">
         <f>SUM(C2:C10)</f>
-        <v>0</v>
+        <v>1711799.87</v>
       </c>
       <c r="D11" s="5">
         <f>SUM(D2:D10)</f>
-        <v>0</v>
+        <v>107952.0</v>
       </c>
       <c r="E11" s="5">
         <f>SUM(E2:E10)</f>
-        <v>0</v>
+        <v>1508567.4</v>
       </c>
       <c r="F11" s="5">
         <f>SUM(F2:F10)</f>
-        <v>0</v>
+        <v>867316.8</v>
       </c>
       <c r="G11" s="5">
         <f>SUM(G2:G10)</f>
-        <v>0</v>
+        <v>13248.12</v>
       </c>
       <c r="H11" s="5">
         <f>SUM(H2:H10)</f>
-        <v>0</v>
+        <v>28187145.87</v>
       </c>
     </row>
     <row r="13" spans="1:10">

--- a/Beacon Superday-Submission/output/Vendor_Readout.xlsx
+++ b/Beacon Superday-Submission/output/Vendor_Readout.xlsx
@@ -11,22 +11,24 @@
     <sheet name="Monthly Value" sheetId="2" r:id="rId2"/>
     <sheet name="Vendor Scorecard" sheetId="3" r:id="rId3"/>
     <sheet name="On-time Trend" sheetId="4" r:id="rId4"/>
-    <sheet name="Past-due Open Lines" sheetId="5" r:id="rId5"/>
-    <sheet name="Price Above PO" sheetId="6" r:id="rId6"/>
-    <sheet name="Revised Confirmations" sheetId="7" r:id="rId7"/>
-    <sheet name="PN Crosswalk" sheetId="8" r:id="rId8"/>
-    <sheet name="Data Quality" sheetId="9" r:id="rId9"/>
-    <sheet name="Definitions" sheetId="10" r:id="rId10"/>
+    <sheet name="Open Orders at Risk" sheetId="5" r:id="rId5"/>
+    <sheet name="Past-due Open Lines" sheetId="6" r:id="rId6"/>
+    <sheet name="Price Above PO" sheetId="7" r:id="rId7"/>
+    <sheet name="Revised Confirmations" sheetId="8" r:id="rId8"/>
+    <sheet name="PN Crosswalk" sheetId="9" r:id="rId9"/>
+    <sheet name="Data Quality" sheetId="10" r:id="rId10"/>
+    <sheet name="Definitions" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Past-due Open Lines'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open Orders at Risk'!$A$3:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Past-due Open Lines'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="515">
   <si>
     <t>Beacon vendor performance readout - ERP history 09/06/2025 to 05/17/2026 (as of 05/17/2026)</t>
   </si>
@@ -85,7 +87,19 @@
     <t>• QuickShip Industrial: the benchmark at 99% on time, but only $13k of spend.</t>
   </si>
   <si>
-    <t>Tabs: Monthly Value | Vendor Scorecard | On-time Trend | Past-due Open Lines | Price Above PO | Revised Confirmations | PN Crosswalk | Data Quality | Definitions</t>
+    <t>LOOKING AHEAD: OPEN ORDERS DUE IN THE NEXT 60 DAYS ($3.32M)</t>
+  </si>
+  <si>
+    <t>• 3 line(s) at high risk of arriving late ($16k): Continental PO-4500050022 L1; Continental PO-4500050023 L1; Heritage PO-4500050012 L1.</t>
+  </si>
+  <si>
+    <t>• 26 line(s) due within 14 days ($1.84M) have no acknowledgment on file - chase them.</t>
+  </si>
+  <si>
+    <t>• Backtest of the same rule on 8 months of history: it flagged 59 of the 63 lines that arrived more than 7 days late; about 1 in 3 flagged lines was late. A watch list, not a prediction.</t>
+  </si>
+  <si>
+    <t>Tabs: Monthly Value | Vendor Scorecard | On-time Trend | Open Orders at Risk | Past-due Open Lines | Price Above PO | Revised Confirmations | PN Crosswalk | Data Quality | Definitions</t>
   </si>
   <si>
     <t>Month</t>
@@ -301,6 +315,12 @@
     <t>2026-05</t>
   </si>
   <si>
+    <t>Open PO lines due 05/18/2026 to 07/16/2026. Flag rule: vendor already promises after our need date, or this vendor delivers this part on time &lt;60% of the time (5+ past lines). Backtest on history: flagged 59 of 63 lines that arrived &gt;7 days late; 33% of flagged lines were late vs 22% overall.</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
     <t>Vendor</t>
   </si>
   <si>
@@ -313,6 +333,423 @@
     <t>Part</t>
   </si>
   <si>
+    <t>Open qty</t>
+  </si>
+  <si>
+    <t>Open $</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Days to due</t>
+  </si>
+  <si>
+    <t>Promised</t>
+  </si>
+  <si>
+    <t>Promise from</t>
+  </si>
+  <si>
+    <t>Vendor+part on time</t>
+  </si>
+  <si>
+    <t>Past lines</t>
+  </si>
+  <si>
+    <t>Why</t>
+  </si>
+  <si>
+    <t>Suggested action</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>PO-4500050022</t>
+  </si>
+  <si>
+    <t>HT-PRECIP</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>This week's acknowledgment</t>
+  </si>
+  <si>
+    <t>vendor promises 21 day(s) after we need it; on time 40% of the last 43 deliveries of this part; we allowed 14 days; this part usually takes 26</t>
+  </si>
+  <si>
+    <t>Ask the vendor for a firm date now; warn planning if the job can't move.</t>
+  </si>
+  <si>
+    <t>PO-4500050023</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>on time 40% of the last 43 deliveries of this part; we allowed 21 days; this part usually takes 26</t>
+  </si>
+  <si>
+    <t>PO-4500050012</t>
+  </si>
+  <si>
+    <t>CHB-9472-4</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>vendor promises 14 day(s) after we need it</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>PO-4500045950</t>
+  </si>
+  <si>
+    <t>BAR-TI64-188</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>None on file</t>
+  </si>
+  <si>
+    <t>no confirmation on file</t>
+  </si>
+  <si>
+    <t>No action.</t>
+  </si>
+  <si>
+    <t>PO-4500045875</t>
+  </si>
+  <si>
+    <t>BAR-A286-250</t>
+  </si>
+  <si>
+    <t>BAR-CRES-250</t>
+  </si>
+  <si>
+    <t>PO-4500050013</t>
+  </si>
+  <si>
+    <t>CHB-7715</t>
+  </si>
+  <si>
+    <t>we allowed 28 days; this part usually takes 33</t>
+  </si>
+  <si>
+    <t>CHB-9472-3</t>
+  </si>
+  <si>
+    <t>we allowed 28 days; this part usually takes 32</t>
+  </si>
+  <si>
+    <t>PO-4500046338</t>
+  </si>
+  <si>
+    <t>CHB-5520</t>
+  </si>
+  <si>
+    <t>PO-4500050032</t>
+  </si>
+  <si>
+    <t>MISC-SPR-001</t>
+  </si>
+  <si>
+    <t>track record and promise look fine</t>
+  </si>
+  <si>
+    <t>MISC-WAS-A25</t>
+  </si>
+  <si>
+    <t>PO-4500045668</t>
+  </si>
+  <si>
+    <t>BAR-A286-375</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>PO-4500047050</t>
+  </si>
+  <si>
+    <t>TOOL-DIE-9472</t>
+  </si>
+  <si>
+    <t>ERP confirmation</t>
+  </si>
+  <si>
+    <t>TOOL-INS-CAR</t>
+  </si>
+  <si>
+    <t>PO-4500050018</t>
+  </si>
+  <si>
+    <t>PLAT-CAD</t>
+  </si>
+  <si>
+    <t>we allowed 10 days; this part usually takes 14</t>
+  </si>
+  <si>
+    <t>PO-4500045787</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>PO-4500046257</t>
+  </si>
+  <si>
+    <t>PO-4500046379</t>
+  </si>
+  <si>
+    <t>PO-4500045910</t>
+  </si>
+  <si>
+    <t>PO-4500050002</t>
+  </si>
+  <si>
+    <t>we allowed 28 days; this part usually takes 39</t>
+  </si>
+  <si>
+    <t>PO-4500050004</t>
+  </si>
+  <si>
+    <t>PO-4500050030</t>
+  </si>
+  <si>
+    <t>PO-4500045585</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>PO-4500045631</t>
+  </si>
+  <si>
+    <t>PO-4500050019</t>
+  </si>
+  <si>
+    <t>PLAT-PASV</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>we allowed 10 days; this part usually takes 15; no confirmation on file</t>
+  </si>
+  <si>
+    <t>PO-4500045702</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>PO-4500046171</t>
+  </si>
+  <si>
+    <t>PO-4500046040</t>
+  </si>
+  <si>
+    <t>PO-4500046297</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>PO-4500045751</t>
+  </si>
+  <si>
+    <t>BAR-4130-312</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>PO-4500046081</t>
+  </si>
+  <si>
+    <t>PO-4500050008</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>we allowed 35 days; this part usually takes 40</t>
+  </si>
+  <si>
+    <t>PO-4500045991</t>
+  </si>
+  <si>
+    <t>PO-4500046220</t>
+  </si>
+  <si>
+    <t>we allowed 35 days; this part usually takes 39</t>
+  </si>
+  <si>
+    <t>PO-4500050017</t>
+  </si>
+  <si>
+    <t>PO-4500047093</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>PO-4500050003</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>we allowed 21 days; this part usually takes 39</t>
+  </si>
+  <si>
+    <t>PO-4500045835</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>PO-4500045543</t>
+  </si>
+  <si>
+    <t>PO-4500045878</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>PO-4500045953</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>PO-4500050011</t>
+  </si>
+  <si>
+    <t>CHB-3301</t>
+  </si>
+  <si>
+    <t>we allowed 28 days; this part usually takes 31</t>
+  </si>
+  <si>
+    <t>PO-4500045792</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>PO-4500050014</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>PO-4500050009</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>PO-4500047137</t>
+  </si>
+  <si>
+    <t>PO-4500045669</t>
+  </si>
+  <si>
+    <t>PO-4500050029</t>
+  </si>
+  <si>
+    <t>we allowed 56 days; this part usually takes 60</t>
+  </si>
+  <si>
+    <t>we allowed 56 days; this part usually takes 61</t>
+  </si>
+  <si>
+    <t>PO-4500050005</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>PO-4500050001</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>PO-4500050028</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>we allowed 42 days; this part usually takes 60</t>
+  </si>
+  <si>
+    <t>PO-4500050006</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>PO-4500047053</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>PO-4500050007</t>
+  </si>
+  <si>
+    <t>TOOL-PUNCH-STD</t>
+  </si>
+  <si>
+    <t>PO-4500050015</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>PO-4500047095</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>PO-4500050010</t>
+  </si>
+  <si>
+    <t>PO-4500047056</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>PO-4500047142</t>
+  </si>
+  <si>
+    <t>PO-4500050026</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
     <t>Ordered</t>
   </si>
   <si>
@@ -325,9 +762,6 @@
     <t>Balance $</t>
   </si>
   <si>
-    <t>Required</t>
-  </si>
-  <si>
     <t>Days past due</t>
   </si>
   <si>
@@ -340,9 +774,6 @@
     <t>PO-4500050027</t>
   </si>
   <si>
-    <t>TOOL-DIE-9472</t>
-  </si>
-  <si>
     <t>2026-05-15</t>
   </si>
   <si>
@@ -352,9 +783,6 @@
     <t>PO-4500045503</t>
   </si>
   <si>
-    <t>BAR-TI64-188</t>
-  </si>
-  <si>
     <t>2025-10-14</t>
   </si>
   <si>
@@ -379,9 +807,6 @@
     <t>PO-4500045662</t>
   </si>
   <si>
-    <t>BAR-A286-375</t>
-  </si>
-  <si>
     <t>2026-04-06</t>
   </si>
   <si>
@@ -397,9 +822,6 @@
     <t>PO-4500045536</t>
   </si>
   <si>
-    <t>BAR-CRES-250</t>
-  </si>
-  <si>
     <t>2026-04-24</t>
   </si>
   <si>
@@ -436,9 +858,6 @@
     <t>PO-4500046185</t>
   </si>
   <si>
-    <t>CHB-5520</t>
-  </si>
-  <si>
     <t>2025-12-10</t>
   </si>
   <si>
@@ -463,21 +882,12 @@
     <t>2026-05-17</t>
   </si>
   <si>
-    <t>BAR-4130-312</t>
-  </si>
-  <si>
     <t>2026-03-04</t>
   </si>
   <si>
-    <t>TOOL-INS-CAR</t>
-  </si>
-  <si>
     <t>PO-4500046202</t>
   </si>
   <si>
-    <t>CHB-9472-3</t>
-  </si>
-  <si>
     <t>2026-02-19</t>
   </si>
   <si>
@@ -487,9 +897,6 @@
     <t>PO-4500046523</t>
   </si>
   <si>
-    <t>PLAT-PASV</t>
-  </si>
-  <si>
     <t>PO-4500046323</t>
   </si>
   <si>
@@ -526,9 +933,6 @@
     <t>PO-4500046226</t>
   </si>
   <si>
-    <t>CHB-3301</t>
-  </si>
-  <si>
     <t>2025-11-06</t>
   </si>
   <si>
@@ -538,9 +942,6 @@
     <t>PO-4500046787</t>
   </si>
   <si>
-    <t>HT-PRECIP</t>
-  </si>
-  <si>
     <t>2025-10-24</t>
   </si>
   <si>
@@ -571,9 +972,6 @@
     <t>PO-4500046419</t>
   </si>
   <si>
-    <t>PLAT-CAD</t>
-  </si>
-  <si>
     <t>2026-03-18</t>
   </si>
   <si>
@@ -619,9 +1017,6 @@
     <t>PO-4500046363</t>
   </si>
   <si>
-    <t>CHB-7715</t>
-  </si>
-  <si>
     <t>2026-02-26</t>
   </si>
   <si>
@@ -631,9 +1026,6 @@
     <t>PO-4500050031</t>
   </si>
   <si>
-    <t>MISC-WAS-A25</t>
-  </si>
-  <si>
     <t>PO-4500046515</t>
   </si>
   <si>
@@ -670,9 +1062,6 @@
     <t>PO-4500047308</t>
   </si>
   <si>
-    <t>MISC-SPR-001</t>
-  </si>
-  <si>
     <t>2026-02-25</t>
   </si>
   <si>
@@ -946,9 +1335,6 @@
     <t>APH-441-OS</t>
   </si>
   <si>
-    <t>CHB-9472-4</t>
-  </si>
-  <si>
     <t>This week's PDF (inferred by qty+price)</t>
   </si>
   <si>
@@ -992,9 +1378,6 @@
   </si>
   <si>
     <t>Seen 41 times, 2025-09-03 to 2026-03-31. Same PN used by another vendor for a different part.</t>
-  </si>
-  <si>
-    <t>TOOL-PUNCH-STD</t>
   </si>
   <si>
     <t>Seen 18 times, 2025-09-14 to 2026-02-27. Same PN used by another vendor for a different part.</t>
@@ -1203,7 +1586,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1235,8 +1618,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1246,6 +1637,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1283,7 +1686,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1298,7 +1701,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2887,7 +3292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="130.7109375" customWidth="1"/>
@@ -2989,8 +3394,28 @@
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2999,6 +3424,179 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="80.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>489</v>
+      </c>
+      <c r="B15" s="5">
+        <v>28187145.87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B16" s="5">
+        <v>29503886.49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B17" s="5">
+        <v>25295562.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B18" s="5">
+        <v>75999.42763999989</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3009,98 +3607,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>366</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>367</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>495</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>369</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>370</v>
+        <v>497</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>371</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>499</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>373</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>375</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>503</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>377</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>505</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>379</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>380</v>
+        <v>507</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>381</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>382</v>
+        <v>509</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>384</v>
+        <v>511</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>385</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>386</v>
+        <v>513</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>387</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -3119,39 +3717,39 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -3183,7 +3781,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5">
         <v>3080026.78</v>
@@ -3215,7 +3813,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>4338652.6</v>
@@ -3247,7 +3845,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5">
         <v>2942700.91</v>
@@ -3279,7 +3877,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5">
         <v>4489089.88</v>
@@ -3311,7 +3909,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5">
         <v>2585747.33</v>
@@ -3343,7 +3941,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>3153715.17</v>
@@ -3375,7 +3973,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5">
         <v>2715925.57</v>
@@ -3407,7 +4005,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B10" s="5">
         <v>672403.4399999999</v>
@@ -3439,7 +4037,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5">
         <f>SUM(B2:B10)</f>
@@ -3472,7 +4070,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3492,30 +4090,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="5">
         <v>23978261.68</v>
@@ -3538,7 +4136,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B3" s="6">
         <v>0.8506807248448812</v>
@@ -3561,7 +4159,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B4" s="7">
         <v>172</v>
@@ -3584,7 +4182,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B5" s="7">
         <v>222</v>
@@ -3607,7 +4205,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B6" s="6">
         <v>0.8693693693693694</v>
@@ -3630,7 +4228,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="7">
         <v>29</v>
@@ -3653,7 +4251,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="7">
         <v>0</v>
@@ -3676,7 +4274,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" s="6">
         <v>0</v>
@@ -3699,7 +4297,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
@@ -3722,7 +4320,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B11" s="5">
         <v>2514198.5</v>
@@ -3745,7 +4343,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8">
         <v>1.827586206896552</v>
@@ -3768,7 +4366,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -3791,7 +4389,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B14" s="7">
         <v>6</v>
@@ -3814,7 +4412,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B15" s="6">
         <v>1</v>
@@ -3837,7 +4435,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B16" s="6">
         <v>0.8378378378378378</v>
@@ -3860,7 +4458,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B17" s="6">
         <v>0.963963963963964</v>
@@ -3883,7 +4481,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B18" s="7">
         <v>209</v>
@@ -3906,7 +4504,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B19" s="6">
         <v>0.1866028708133971</v>
@@ -3929,7 +4527,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B20" s="8">
         <v>0.2344497607655502</v>
@@ -3952,7 +4550,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B21" s="6">
         <v>0.8899521531100478</v>
@@ -3975,7 +4573,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B22" s="8">
         <v>42</v>
@@ -3998,7 +4596,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" s="8">
         <v>42</v>
@@ -4021,7 +4619,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B24" s="8">
         <v>40</v>
@@ -4044,7 +4642,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B25" s="6">
         <v>0.4864864864864865</v>
@@ -4067,7 +4665,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B26" s="6">
         <v>0.95</v>
@@ -4090,7 +4688,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B27" s="7">
         <v>7</v>
@@ -4113,7 +4711,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B28" s="7">
         <v>4</v>
@@ -4136,7 +4734,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B29" s="7">
         <v>8</v>
@@ -4159,7 +4757,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B30" s="5">
         <v>76706.32000000001</v>
@@ -4182,7 +4780,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -4205,7 +4803,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B32" s="7">
         <v>8</v>
@@ -4228,7 +4826,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B33" s="7">
         <v>11</v>
@@ -4251,7 +4849,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B34" s="5">
         <v>8522.080000000027</v>
@@ -4274,7 +4872,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B35" s="7">
         <v>9</v>
@@ -4297,7 +4895,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B36" s="7">
         <v>2</v>
@@ -4320,7 +4918,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B37" s="8">
         <v>6.040268456375839</v>
@@ -4343,7 +4941,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B38" s="6">
         <v>0.8666666666666667</v>
@@ -4366,7 +4964,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B39" s="7">
         <v>90</v>
@@ -4389,7 +4987,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6">
         <v>0.8712121212121212</v>
@@ -4412,7 +5010,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B41" s="7">
         <v>132</v>
@@ -4435,7 +5033,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B42" s="9">
         <v>1</v>
@@ -4477,48 +5075,48 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F2" s="6">
         <v>0.9230769230769231</v>
@@ -4541,7 +5139,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6">
         <v>0.8095238095238095</v>
@@ -4576,7 +5174,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" s="6">
         <v>0.8378378378378378</v>
@@ -4617,7 +5215,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" s="6">
         <v>0.9375</v>
@@ -4658,7 +5256,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B6" s="6">
         <v>0.8</v>
@@ -4699,7 +5297,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6">
         <v>0.8888888888888888</v>
@@ -4740,7 +5338,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6">
         <v>0.8529411764705882</v>
@@ -4781,7 +5379,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" s="6">
         <v>0.896551724137931</v>
@@ -4822,7 +5420,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
@@ -4868,6 +5466,3716 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O83"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
+    <col min="14" max="14" width="60.7109375" customWidth="1"/>
+    <col min="15" max="15" width="45.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="45" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.3953488372093023</v>
+      </c>
+      <c r="M4">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5">
+        <v>750</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1800</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.3953488372093023</v>
+      </c>
+      <c r="M5">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6">
+        <v>15000</v>
+      </c>
+      <c r="G6" s="5">
+        <v>12900</v>
+      </c>
+      <c r="H6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.775</v>
+      </c>
+      <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6" t="s">
+        <v>126</v>
+      </c>
+      <c r="O6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7">
+        <v>14600</v>
+      </c>
+      <c r="G7" s="5">
+        <v>328500</v>
+      </c>
+      <c r="H7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="M7">
+        <v>46</v>
+      </c>
+      <c r="N7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8">
+        <v>16200</v>
+      </c>
+      <c r="G8" s="5">
+        <v>76302</v>
+      </c>
+      <c r="H8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M8">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9">
+        <v>17000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>66640</v>
+      </c>
+      <c r="H9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M9">
+        <v>42</v>
+      </c>
+      <c r="N9" t="s">
+        <v>132</v>
+      </c>
+      <c r="O9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10">
+        <v>25000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>15500</v>
+      </c>
+      <c r="H10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" t="s">
+        <v>116</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M10">
+        <v>46</v>
+      </c>
+      <c r="N10" t="s">
+        <v>139</v>
+      </c>
+      <c r="O10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" t="s">
+        <v>116</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M11">
+        <v>34</v>
+      </c>
+      <c r="N11" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12">
+        <v>3800</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2090</v>
+      </c>
+      <c r="H12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0.6595744680851063</v>
+      </c>
+      <c r="M12">
+        <v>47</v>
+      </c>
+      <c r="N12" t="s">
+        <v>132</v>
+      </c>
+      <c r="O12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="5">
+        <v>180</v>
+      </c>
+      <c r="H13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="6">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>41</v>
+      </c>
+      <c r="N13" t="s">
+        <v>146</v>
+      </c>
+      <c r="O13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14">
+        <v>500</v>
+      </c>
+      <c r="G14" s="5">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="6">
+        <v>0.972972972972973</v>
+      </c>
+      <c r="M14">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>146</v>
+      </c>
+      <c r="O14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15">
+        <v>22500</v>
+      </c>
+      <c r="G15" s="5">
+        <v>176400</v>
+      </c>
+      <c r="H15" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M15">
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>132</v>
+      </c>
+      <c r="O15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16">
+        <v>23400</v>
+      </c>
+      <c r="G16" s="5">
+        <v>91728</v>
+      </c>
+      <c r="H16" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M16">
+        <v>42</v>
+      </c>
+      <c r="N16" t="s">
+        <v>132</v>
+      </c>
+      <c r="O16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5">
+        <v>13640</v>
+      </c>
+      <c r="H17" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M17">
+        <v>20</v>
+      </c>
+      <c r="N17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18">
+        <v>27</v>
+      </c>
+      <c r="G18" s="5">
+        <v>491.4</v>
+      </c>
+      <c r="H18" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" t="s">
+        <v>153</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18" t="s">
+        <v>146</v>
+      </c>
+      <c r="O18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19">
+        <v>2500</v>
+      </c>
+      <c r="G19" s="5">
+        <v>275</v>
+      </c>
+      <c r="H19" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" t="s">
+        <v>116</v>
+      </c>
+      <c r="L19" s="6">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="M19">
+        <v>65</v>
+      </c>
+      <c r="N19" t="s">
+        <v>157</v>
+      </c>
+      <c r="O19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20">
+        <v>12800</v>
+      </c>
+      <c r="G20" s="5">
+        <v>100352</v>
+      </c>
+      <c r="H20" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="K20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M20">
+        <v>50</v>
+      </c>
+      <c r="N20" t="s">
+        <v>132</v>
+      </c>
+      <c r="O20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21">
+        <v>19700</v>
+      </c>
+      <c r="G21" s="5">
+        <v>77224</v>
+      </c>
+      <c r="H21" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="K21" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M21">
+        <v>42</v>
+      </c>
+      <c r="N21" t="s">
+        <v>132</v>
+      </c>
+      <c r="O21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22">
+        <v>18700</v>
+      </c>
+      <c r="G22" s="5">
+        <v>10285</v>
+      </c>
+      <c r="H22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="K22" t="s">
+        <v>131</v>
+      </c>
+      <c r="L22" s="6">
+        <v>0.6595744680851063</v>
+      </c>
+      <c r="M22">
+        <v>47</v>
+      </c>
+      <c r="N22" t="s">
+        <v>132</v>
+      </c>
+      <c r="O22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23">
+        <v>9400</v>
+      </c>
+      <c r="G23" s="5">
+        <v>7896</v>
+      </c>
+      <c r="H23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>131</v>
+      </c>
+      <c r="L23" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M23">
+        <v>34</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24">
+        <v>3000</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2580</v>
+      </c>
+      <c r="H24" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>131</v>
+      </c>
+      <c r="L24" s="6">
+        <v>0.775</v>
+      </c>
+      <c r="M24">
+        <v>40</v>
+      </c>
+      <c r="N24" t="s">
+        <v>132</v>
+      </c>
+      <c r="O24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25">
+        <v>3900</v>
+      </c>
+      <c r="G25" s="5">
+        <v>87750</v>
+      </c>
+      <c r="H25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+      <c r="K25" t="s">
+        <v>131</v>
+      </c>
+      <c r="L25" s="6">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="M25">
+        <v>46</v>
+      </c>
+      <c r="N25" t="s">
+        <v>132</v>
+      </c>
+      <c r="O25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="5">
+        <v>3920</v>
+      </c>
+      <c r="H26" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>114</v>
+      </c>
+      <c r="K26" t="s">
+        <v>116</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M26">
+        <v>42</v>
+      </c>
+      <c r="N26" t="s">
+        <v>164</v>
+      </c>
+      <c r="O26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27">
+        <v>200</v>
+      </c>
+      <c r="G27" s="5">
+        <v>942</v>
+      </c>
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K27" t="s">
+        <v>116</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M27">
+        <v>45</v>
+      </c>
+      <c r="N27" t="s">
+        <v>164</v>
+      </c>
+      <c r="O27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28">
+        <v>500</v>
+      </c>
+      <c r="G28" s="5">
+        <v>90</v>
+      </c>
+      <c r="H28" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" t="s">
+        <v>116</v>
+      </c>
+      <c r="L28" s="6">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>41</v>
+      </c>
+      <c r="N28" t="s">
+        <v>146</v>
+      </c>
+      <c r="O28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29">
+        <v>23400</v>
+      </c>
+      <c r="G29" s="5">
+        <v>110214</v>
+      </c>
+      <c r="H29" t="s">
+        <v>168</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="K29" t="s">
+        <v>131</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M29">
+        <v>45</v>
+      </c>
+      <c r="N29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30">
+        <v>17000</v>
+      </c>
+      <c r="G30" s="5">
+        <v>66640</v>
+      </c>
+      <c r="H30" t="s">
+        <v>168</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>131</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M30">
+        <v>42</v>
+      </c>
+      <c r="N30" t="s">
+        <v>132</v>
+      </c>
+      <c r="O30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31">
+        <v>25000</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31">
+        <v>7</v>
+      </c>
+      <c r="K31" t="s">
+        <v>131</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="M31">
+        <v>62</v>
+      </c>
+      <c r="N31" t="s">
+        <v>173</v>
+      </c>
+      <c r="O31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32">
+        <v>23400</v>
+      </c>
+      <c r="G32" s="5">
+        <v>526500</v>
+      </c>
+      <c r="H32" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="K32" t="s">
+        <v>131</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="M32">
+        <v>46</v>
+      </c>
+      <c r="N32" t="s">
+        <v>132</v>
+      </c>
+      <c r="O32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33">
+        <v>20900</v>
+      </c>
+      <c r="G33" s="5">
+        <v>12958</v>
+      </c>
+      <c r="H33" t="s">
+        <v>175</v>
+      </c>
+      <c r="I33">
+        <v>8</v>
+      </c>
+      <c r="K33" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M33">
+        <v>46</v>
+      </c>
+      <c r="N33" t="s">
+        <v>132</v>
+      </c>
+      <c r="O33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34">
+        <v>21400</v>
+      </c>
+      <c r="G34" s="5">
+        <v>11770</v>
+      </c>
+      <c r="H34" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34">
+        <v>8</v>
+      </c>
+      <c r="K34" t="s">
+        <v>131</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.6595744680851063</v>
+      </c>
+      <c r="M34">
+        <v>47</v>
+      </c>
+      <c r="N34" t="s">
+        <v>132</v>
+      </c>
+      <c r="O34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35">
+        <v>14400</v>
+      </c>
+      <c r="G35" s="5">
+        <v>8928</v>
+      </c>
+      <c r="H35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35">
+        <v>9</v>
+      </c>
+      <c r="K35" t="s">
+        <v>131</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M35">
+        <v>46</v>
+      </c>
+      <c r="N35" t="s">
+        <v>132</v>
+      </c>
+      <c r="O35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36">
+        <v>9500</v>
+      </c>
+      <c r="G36" s="5">
+        <v>8170</v>
+      </c>
+      <c r="H36" t="s">
+        <v>179</v>
+      </c>
+      <c r="I36">
+        <v>9</v>
+      </c>
+      <c r="K36" t="s">
+        <v>131</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.775</v>
+      </c>
+      <c r="M36">
+        <v>40</v>
+      </c>
+      <c r="N36" t="s">
+        <v>132</v>
+      </c>
+      <c r="O36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37">
+        <v>6500</v>
+      </c>
+      <c r="G37" s="5">
+        <v>18525</v>
+      </c>
+      <c r="H37" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="K37" t="s">
+        <v>131</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="M37">
+        <v>39</v>
+      </c>
+      <c r="N37" t="s">
+        <v>132</v>
+      </c>
+      <c r="O37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F38">
+        <v>20700</v>
+      </c>
+      <c r="G38" s="5">
+        <v>12834</v>
+      </c>
+      <c r="H38" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38">
+        <v>10</v>
+      </c>
+      <c r="K38" t="s">
+        <v>131</v>
+      </c>
+      <c r="L38" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M38">
+        <v>46</v>
+      </c>
+      <c r="N38" t="s">
+        <v>132</v>
+      </c>
+      <c r="O38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39">
+        <v>600</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2826</v>
+      </c>
+      <c r="H39" t="s">
+        <v>182</v>
+      </c>
+      <c r="I39">
+        <v>10</v>
+      </c>
+      <c r="K39" t="s">
+        <v>131</v>
+      </c>
+      <c r="L39" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M39">
+        <v>45</v>
+      </c>
+      <c r="N39" t="s">
+        <v>132</v>
+      </c>
+      <c r="O39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40">
+        <v>600</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2352</v>
+      </c>
+      <c r="H40" t="s">
+        <v>182</v>
+      </c>
+      <c r="I40">
+        <v>10</v>
+      </c>
+      <c r="K40" t="s">
+        <v>131</v>
+      </c>
+      <c r="L40" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M40">
+        <v>42</v>
+      </c>
+      <c r="N40" t="s">
+        <v>132</v>
+      </c>
+      <c r="O40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41">
+        <v>1000</v>
+      </c>
+      <c r="G41" s="5">
+        <v>22500</v>
+      </c>
+      <c r="H41" t="s">
+        <v>185</v>
+      </c>
+      <c r="I41">
+        <v>11</v>
+      </c>
+      <c r="J41" t="s">
+        <v>185</v>
+      </c>
+      <c r="K41" t="s">
+        <v>116</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="M41">
+        <v>46</v>
+      </c>
+      <c r="N41" t="s">
+        <v>186</v>
+      </c>
+      <c r="O41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42">
+        <v>21700</v>
+      </c>
+      <c r="G42" s="5">
+        <v>18228</v>
+      </c>
+      <c r="H42" t="s">
+        <v>185</v>
+      </c>
+      <c r="I42">
+        <v>11</v>
+      </c>
+      <c r="K42" t="s">
+        <v>131</v>
+      </c>
+      <c r="L42" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M42">
+        <v>34</v>
+      </c>
+      <c r="N42" t="s">
+        <v>132</v>
+      </c>
+      <c r="O42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43">
+        <v>18500</v>
+      </c>
+      <c r="G43" s="5">
+        <v>11470</v>
+      </c>
+      <c r="H43" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43">
+        <v>11</v>
+      </c>
+      <c r="K43" t="s">
+        <v>131</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M43">
+        <v>46</v>
+      </c>
+      <c r="N43" t="s">
+        <v>132</v>
+      </c>
+      <c r="O43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>135</v>
+      </c>
+      <c r="F44">
+        <v>1000</v>
+      </c>
+      <c r="G44" s="5">
+        <v>4710</v>
+      </c>
+      <c r="H44" t="s">
+        <v>185</v>
+      </c>
+      <c r="I44">
+        <v>11</v>
+      </c>
+      <c r="J44" t="s">
+        <v>185</v>
+      </c>
+      <c r="K44" t="s">
+        <v>116</v>
+      </c>
+      <c r="L44" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M44">
+        <v>45</v>
+      </c>
+      <c r="N44" t="s">
+        <v>189</v>
+      </c>
+      <c r="O44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>156</v>
+      </c>
+      <c r="F45">
+        <v>2500</v>
+      </c>
+      <c r="G45" s="5">
+        <v>275</v>
+      </c>
+      <c r="H45" t="s">
+        <v>185</v>
+      </c>
+      <c r="I45">
+        <v>11</v>
+      </c>
+      <c r="J45" t="s">
+        <v>185</v>
+      </c>
+      <c r="K45" t="s">
+        <v>116</v>
+      </c>
+      <c r="L45" s="6">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="M45">
+        <v>65</v>
+      </c>
+      <c r="N45" t="s">
+        <v>146</v>
+      </c>
+      <c r="O45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46">
+        <v>37</v>
+      </c>
+      <c r="G46" s="5">
+        <v>45880</v>
+      </c>
+      <c r="H46" t="s">
+        <v>192</v>
+      </c>
+      <c r="I46">
+        <v>12</v>
+      </c>
+      <c r="J46" t="s">
+        <v>192</v>
+      </c>
+      <c r="K46" t="s">
+        <v>153</v>
+      </c>
+      <c r="L46" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M46">
+        <v>20</v>
+      </c>
+      <c r="N46" t="s">
+        <v>146</v>
+      </c>
+      <c r="O46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>193</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47">
+        <v>1500</v>
+      </c>
+      <c r="G47" s="5">
+        <v>5880</v>
+      </c>
+      <c r="H47" t="s">
+        <v>194</v>
+      </c>
+      <c r="I47">
+        <v>13</v>
+      </c>
+      <c r="J47" t="s">
+        <v>194</v>
+      </c>
+      <c r="K47" t="s">
+        <v>116</v>
+      </c>
+      <c r="L47" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M47">
+        <v>42</v>
+      </c>
+      <c r="N47" t="s">
+        <v>195</v>
+      </c>
+      <c r="O47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48">
+        <v>18000</v>
+      </c>
+      <c r="G48" s="5">
+        <v>405000</v>
+      </c>
+      <c r="H48" t="s">
+        <v>197</v>
+      </c>
+      <c r="I48">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>131</v>
+      </c>
+      <c r="L48" s="6">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="M48">
+        <v>46</v>
+      </c>
+      <c r="N48" t="s">
+        <v>132</v>
+      </c>
+      <c r="O48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>135</v>
+      </c>
+      <c r="F49">
+        <v>18800</v>
+      </c>
+      <c r="G49" s="5">
+        <v>88548</v>
+      </c>
+      <c r="H49" t="s">
+        <v>197</v>
+      </c>
+      <c r="I49">
+        <v>15</v>
+      </c>
+      <c r="K49" t="s">
+        <v>131</v>
+      </c>
+      <c r="L49" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M49">
+        <v>45</v>
+      </c>
+      <c r="N49" t="s">
+        <v>132</v>
+      </c>
+      <c r="O49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F50">
+        <v>20000</v>
+      </c>
+      <c r="G50" s="5">
+        <v>78400</v>
+      </c>
+      <c r="H50" t="s">
+        <v>197</v>
+      </c>
+      <c r="I50">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>131</v>
+      </c>
+      <c r="L50" s="6">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="M50">
+        <v>42</v>
+      </c>
+      <c r="N50" t="s">
+        <v>132</v>
+      </c>
+      <c r="O50" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F51">
+        <v>1100</v>
+      </c>
+      <c r="G51" s="5">
+        <v>8624</v>
+      </c>
+      <c r="H51" t="s">
+        <v>197</v>
+      </c>
+      <c r="I51">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
+        <v>131</v>
+      </c>
+      <c r="L51" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M51">
+        <v>50</v>
+      </c>
+      <c r="N51" t="s">
+        <v>132</v>
+      </c>
+      <c r="O51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>135</v>
+      </c>
+      <c r="F52">
+        <v>16100</v>
+      </c>
+      <c r="G52" s="5">
+        <v>75831</v>
+      </c>
+      <c r="H52" t="s">
+        <v>200</v>
+      </c>
+      <c r="I52">
+        <v>16</v>
+      </c>
+      <c r="K52" t="s">
+        <v>131</v>
+      </c>
+      <c r="L52" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M52">
+        <v>45</v>
+      </c>
+      <c r="N52" t="s">
+        <v>132</v>
+      </c>
+      <c r="O52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>135</v>
+      </c>
+      <c r="F53">
+        <v>14200</v>
+      </c>
+      <c r="G53" s="5">
+        <v>66882</v>
+      </c>
+      <c r="H53" t="s">
+        <v>202</v>
+      </c>
+      <c r="I53">
+        <v>17</v>
+      </c>
+      <c r="K53" t="s">
+        <v>131</v>
+      </c>
+      <c r="L53" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M53">
+        <v>45</v>
+      </c>
+      <c r="N53" t="s">
+        <v>132</v>
+      </c>
+      <c r="O53" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>138</v>
+      </c>
+      <c r="F54">
+        <v>25000</v>
+      </c>
+      <c r="G54" s="5">
+        <v>15500</v>
+      </c>
+      <c r="H54" t="s">
+        <v>124</v>
+      </c>
+      <c r="I54">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s">
+        <v>124</v>
+      </c>
+      <c r="K54" t="s">
+        <v>116</v>
+      </c>
+      <c r="L54" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M54">
+        <v>46</v>
+      </c>
+      <c r="N54" t="s">
+        <v>139</v>
+      </c>
+      <c r="O54" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>204</v>
+      </c>
+      <c r="F55">
+        <v>25000</v>
+      </c>
+      <c r="G55" s="5">
+        <v>10250</v>
+      </c>
+      <c r="H55" t="s">
+        <v>124</v>
+      </c>
+      <c r="I55">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s">
+        <v>124</v>
+      </c>
+      <c r="K55" t="s">
+        <v>116</v>
+      </c>
+      <c r="L55" s="6">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="M55">
+        <v>38</v>
+      </c>
+      <c r="N55" t="s">
+        <v>205</v>
+      </c>
+      <c r="O55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56">
+        <v>5000</v>
+      </c>
+      <c r="G56" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H56" t="s">
+        <v>124</v>
+      </c>
+      <c r="I56">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s">
+        <v>124</v>
+      </c>
+      <c r="K56" t="s">
+        <v>116</v>
+      </c>
+      <c r="L56" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M56">
+        <v>34</v>
+      </c>
+      <c r="N56" t="s">
+        <v>141</v>
+      </c>
+      <c r="O56" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>149</v>
+      </c>
+      <c r="F57">
+        <v>22800</v>
+      </c>
+      <c r="G57" s="5">
+        <v>178752</v>
+      </c>
+      <c r="H57" t="s">
+        <v>207</v>
+      </c>
+      <c r="I57">
+        <v>19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>131</v>
+      </c>
+      <c r="L57" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M57">
+        <v>50</v>
+      </c>
+      <c r="N57" t="s">
+        <v>132</v>
+      </c>
+      <c r="O57" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>140</v>
+      </c>
+      <c r="F58">
+        <v>25000</v>
+      </c>
+      <c r="G58" s="5">
+        <v>21000</v>
+      </c>
+      <c r="H58" t="s">
+        <v>209</v>
+      </c>
+      <c r="I58">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>209</v>
+      </c>
+      <c r="K58" t="s">
+        <v>116</v>
+      </c>
+      <c r="L58" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M58">
+        <v>34</v>
+      </c>
+      <c r="N58" t="s">
+        <v>146</v>
+      </c>
+      <c r="O58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59">
+        <v>25000</v>
+      </c>
+      <c r="G59" s="5">
+        <v>10250</v>
+      </c>
+      <c r="H59" t="s">
+        <v>209</v>
+      </c>
+      <c r="I59">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>209</v>
+      </c>
+      <c r="K59" t="s">
+        <v>116</v>
+      </c>
+      <c r="L59" s="6">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="M59">
+        <v>38</v>
+      </c>
+      <c r="N59" t="s">
+        <v>146</v>
+      </c>
+      <c r="O59" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60">
+        <v>10000</v>
+      </c>
+      <c r="G60" s="5">
+        <v>6200</v>
+      </c>
+      <c r="H60" t="s">
+        <v>209</v>
+      </c>
+      <c r="I60">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>209</v>
+      </c>
+      <c r="K60" t="s">
+        <v>116</v>
+      </c>
+      <c r="L60" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M60">
+        <v>46</v>
+      </c>
+      <c r="N60" t="s">
+        <v>146</v>
+      </c>
+      <c r="O60" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61">
+        <v>50000</v>
+      </c>
+      <c r="G61" s="5">
+        <v>42000</v>
+      </c>
+      <c r="H61" t="s">
+        <v>211</v>
+      </c>
+      <c r="I61">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s">
+        <v>211</v>
+      </c>
+      <c r="K61" t="s">
+        <v>116</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M61">
+        <v>34</v>
+      </c>
+      <c r="N61" t="s">
+        <v>146</v>
+      </c>
+      <c r="O61" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>212</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62">
+        <v>12</v>
+      </c>
+      <c r="G62" s="5">
+        <v>14880</v>
+      </c>
+      <c r="H62" t="s">
+        <v>211</v>
+      </c>
+      <c r="I62">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s">
+        <v>131</v>
+      </c>
+      <c r="L62" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M62">
+        <v>20</v>
+      </c>
+      <c r="N62" t="s">
+        <v>146</v>
+      </c>
+      <c r="O62" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>213</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>181</v>
+      </c>
+      <c r="F63">
+        <v>4700</v>
+      </c>
+      <c r="G63" s="5">
+        <v>13395</v>
+      </c>
+      <c r="H63" t="s">
+        <v>211</v>
+      </c>
+      <c r="I63">
+        <v>22</v>
+      </c>
+      <c r="K63" t="s">
+        <v>131</v>
+      </c>
+      <c r="L63" s="6">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="M63">
+        <v>39</v>
+      </c>
+      <c r="N63" t="s">
+        <v>146</v>
+      </c>
+      <c r="O63" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>152</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64" s="5">
+        <v>6200</v>
+      </c>
+      <c r="H64" t="s">
+        <v>211</v>
+      </c>
+      <c r="I64">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s">
+        <v>211</v>
+      </c>
+      <c r="K64" t="s">
+        <v>116</v>
+      </c>
+      <c r="L64" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M64">
+        <v>20</v>
+      </c>
+      <c r="N64" t="s">
+        <v>215</v>
+      </c>
+      <c r="O64" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>214</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>154</v>
+      </c>
+      <c r="F65">
+        <v>250</v>
+      </c>
+      <c r="G65" s="5">
+        <v>4550</v>
+      </c>
+      <c r="H65" t="s">
+        <v>211</v>
+      </c>
+      <c r="I65">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>211</v>
+      </c>
+      <c r="K65" t="s">
+        <v>116</v>
+      </c>
+      <c r="L65" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M65">
+        <v>15</v>
+      </c>
+      <c r="N65" t="s">
+        <v>216</v>
+      </c>
+      <c r="O65" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>135</v>
+      </c>
+      <c r="F66">
+        <v>1500</v>
+      </c>
+      <c r="G66" s="5">
+        <v>7065</v>
+      </c>
+      <c r="H66" t="s">
+        <v>218</v>
+      </c>
+      <c r="I66">
+        <v>23</v>
+      </c>
+      <c r="J66" t="s">
+        <v>218</v>
+      </c>
+      <c r="K66" t="s">
+        <v>116</v>
+      </c>
+      <c r="L66" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M66">
+        <v>45</v>
+      </c>
+      <c r="N66" t="s">
+        <v>164</v>
+      </c>
+      <c r="O66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>149</v>
+      </c>
+      <c r="F67">
+        <v>2500</v>
+      </c>
+      <c r="G67" s="5">
+        <v>19600</v>
+      </c>
+      <c r="H67" t="s">
+        <v>220</v>
+      </c>
+      <c r="I67">
+        <v>24</v>
+      </c>
+      <c r="J67" t="s">
+        <v>220</v>
+      </c>
+      <c r="K67" t="s">
+        <v>116</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M67">
+        <v>50</v>
+      </c>
+      <c r="N67" t="s">
+        <v>146</v>
+      </c>
+      <c r="O67" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+      <c r="E68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68">
+        <v>1500</v>
+      </c>
+      <c r="G68" s="5">
+        <v>7065</v>
+      </c>
+      <c r="H68" t="s">
+        <v>220</v>
+      </c>
+      <c r="I68">
+        <v>24</v>
+      </c>
+      <c r="K68" t="s">
+        <v>131</v>
+      </c>
+      <c r="L68" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M68">
+        <v>45</v>
+      </c>
+      <c r="N68" t="s">
+        <v>146</v>
+      </c>
+      <c r="O68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>152</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69" s="5">
+        <v>6200</v>
+      </c>
+      <c r="H69" t="s">
+        <v>222</v>
+      </c>
+      <c r="I69">
+        <v>27</v>
+      </c>
+      <c r="J69" t="s">
+        <v>222</v>
+      </c>
+      <c r="K69" t="s">
+        <v>116</v>
+      </c>
+      <c r="L69" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M69">
+        <v>20</v>
+      </c>
+      <c r="N69" t="s">
+        <v>223</v>
+      </c>
+      <c r="O69" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>149</v>
+      </c>
+      <c r="F70">
+        <v>5000</v>
+      </c>
+      <c r="G70" s="5">
+        <v>39200</v>
+      </c>
+      <c r="H70" t="s">
+        <v>225</v>
+      </c>
+      <c r="I70">
+        <v>28</v>
+      </c>
+      <c r="J70" t="s">
+        <v>225</v>
+      </c>
+      <c r="K70" t="s">
+        <v>116</v>
+      </c>
+      <c r="L70" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="M70">
+        <v>50</v>
+      </c>
+      <c r="N70" t="s">
+        <v>146</v>
+      </c>
+      <c r="O70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>226</v>
+      </c>
+      <c r="D71">
+        <v>3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71">
+        <v>58</v>
+      </c>
+      <c r="G71" s="5">
+        <v>71920</v>
+      </c>
+      <c r="H71" t="s">
+        <v>227</v>
+      </c>
+      <c r="I71">
+        <v>29</v>
+      </c>
+      <c r="K71" t="s">
+        <v>131</v>
+      </c>
+      <c r="L71" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M71">
+        <v>20</v>
+      </c>
+      <c r="N71" t="s">
+        <v>146</v>
+      </c>
+      <c r="O71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s">
+        <v>228</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>135</v>
+      </c>
+      <c r="F72">
+        <v>1500</v>
+      </c>
+      <c r="G72" s="5">
+        <v>7065</v>
+      </c>
+      <c r="H72" t="s">
+        <v>227</v>
+      </c>
+      <c r="I72">
+        <v>29</v>
+      </c>
+      <c r="J72" t="s">
+        <v>227</v>
+      </c>
+      <c r="K72" t="s">
+        <v>116</v>
+      </c>
+      <c r="L72" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M72">
+        <v>45</v>
+      </c>
+      <c r="N72" t="s">
+        <v>146</v>
+      </c>
+      <c r="O72" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>226</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>229</v>
+      </c>
+      <c r="F73">
+        <v>58</v>
+      </c>
+      <c r="G73" s="5">
+        <v>5568</v>
+      </c>
+      <c r="H73" t="s">
+        <v>227</v>
+      </c>
+      <c r="I73">
+        <v>29</v>
+      </c>
+      <c r="K73" t="s">
+        <v>131</v>
+      </c>
+      <c r="L73" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="M73">
+        <v>20</v>
+      </c>
+      <c r="N73" t="s">
+        <v>146</v>
+      </c>
+      <c r="O73" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>226</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74">
+        <v>29</v>
+      </c>
+      <c r="G74" s="5">
+        <v>527.8</v>
+      </c>
+      <c r="H74" t="s">
+        <v>227</v>
+      </c>
+      <c r="I74">
+        <v>29</v>
+      </c>
+      <c r="K74" t="s">
+        <v>131</v>
+      </c>
+      <c r="L74" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M74">
+        <v>15</v>
+      </c>
+      <c r="N74" t="s">
+        <v>146</v>
+      </c>
+      <c r="O74" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>123</v>
+      </c>
+      <c r="F75">
+        <v>25000</v>
+      </c>
+      <c r="G75" s="5">
+        <v>21500</v>
+      </c>
+      <c r="H75" t="s">
+        <v>231</v>
+      </c>
+      <c r="I75">
+        <v>31</v>
+      </c>
+      <c r="J75" t="s">
+        <v>231</v>
+      </c>
+      <c r="K75" t="s">
+        <v>116</v>
+      </c>
+      <c r="L75" s="6">
+        <v>0.775</v>
+      </c>
+      <c r="M75">
+        <v>40</v>
+      </c>
+      <c r="N75" t="s">
+        <v>146</v>
+      </c>
+      <c r="O75" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>230</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76" t="s">
+        <v>138</v>
+      </c>
+      <c r="F76">
+        <v>25000</v>
+      </c>
+      <c r="G76" s="5">
+        <v>15500</v>
+      </c>
+      <c r="H76" t="s">
+        <v>231</v>
+      </c>
+      <c r="I76">
+        <v>31</v>
+      </c>
+      <c r="J76" t="s">
+        <v>231</v>
+      </c>
+      <c r="K76" t="s">
+        <v>116</v>
+      </c>
+      <c r="L76" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M76">
+        <v>46</v>
+      </c>
+      <c r="N76" t="s">
+        <v>146</v>
+      </c>
+      <c r="O76" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>230</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77">
+        <v>5000</v>
+      </c>
+      <c r="G77" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H77" t="s">
+        <v>231</v>
+      </c>
+      <c r="I77">
+        <v>31</v>
+      </c>
+      <c r="J77" t="s">
+        <v>231</v>
+      </c>
+      <c r="K77" t="s">
+        <v>116</v>
+      </c>
+      <c r="L77" s="6">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="M77">
+        <v>34</v>
+      </c>
+      <c r="N77" t="s">
+        <v>146</v>
+      </c>
+      <c r="O77" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>232</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78">
+        <v>38</v>
+      </c>
+      <c r="G78" s="5">
+        <v>47120</v>
+      </c>
+      <c r="H78" t="s">
+        <v>233</v>
+      </c>
+      <c r="I78">
+        <v>37</v>
+      </c>
+      <c r="K78" t="s">
+        <v>131</v>
+      </c>
+      <c r="L78" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M78">
+        <v>20</v>
+      </c>
+      <c r="N78" t="s">
+        <v>146</v>
+      </c>
+      <c r="O78" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79">
+        <v>25000</v>
+      </c>
+      <c r="G79" s="5">
+        <v>15500</v>
+      </c>
+      <c r="H79" t="s">
+        <v>233</v>
+      </c>
+      <c r="I79">
+        <v>37</v>
+      </c>
+      <c r="J79" t="s">
+        <v>233</v>
+      </c>
+      <c r="K79" t="s">
+        <v>116</v>
+      </c>
+      <c r="L79" s="6">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M79">
+        <v>46</v>
+      </c>
+      <c r="N79" t="s">
+        <v>146</v>
+      </c>
+      <c r="O79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>229</v>
+      </c>
+      <c r="F80">
+        <v>19</v>
+      </c>
+      <c r="G80" s="5">
+        <v>1824</v>
+      </c>
+      <c r="H80" t="s">
+        <v>233</v>
+      </c>
+      <c r="I80">
+        <v>37</v>
+      </c>
+      <c r="K80" t="s">
+        <v>131</v>
+      </c>
+      <c r="L80" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="M80">
+        <v>20</v>
+      </c>
+      <c r="N80" t="s">
+        <v>146</v>
+      </c>
+      <c r="O80" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>235</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>152</v>
+      </c>
+      <c r="F81">
+        <v>16</v>
+      </c>
+      <c r="G81" s="5">
+        <v>19840</v>
+      </c>
+      <c r="H81" t="s">
+        <v>236</v>
+      </c>
+      <c r="I81">
+        <v>39</v>
+      </c>
+      <c r="K81" t="s">
+        <v>131</v>
+      </c>
+      <c r="L81" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="M81">
+        <v>20</v>
+      </c>
+      <c r="N81" t="s">
+        <v>146</v>
+      </c>
+      <c r="O81" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>237</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>154</v>
+      </c>
+      <c r="F82">
+        <v>4</v>
+      </c>
+      <c r="G82" s="5">
+        <v>72.8</v>
+      </c>
+      <c r="H82" t="s">
+        <v>236</v>
+      </c>
+      <c r="I82">
+        <v>39</v>
+      </c>
+      <c r="K82" t="s">
+        <v>131</v>
+      </c>
+      <c r="L82" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M82">
+        <v>15</v>
+      </c>
+      <c r="N82" t="s">
+        <v>146</v>
+      </c>
+      <c r="O82" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>238</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>154</v>
+      </c>
+      <c r="F83">
+        <v>250</v>
+      </c>
+      <c r="G83" s="5">
+        <v>4550</v>
+      </c>
+      <c r="H83" t="s">
+        <v>239</v>
+      </c>
+      <c r="I83">
+        <v>46</v>
+      </c>
+      <c r="J83" t="s">
+        <v>239</v>
+      </c>
+      <c r="K83" t="s">
+        <v>116</v>
+      </c>
+      <c r="L83" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="M83">
+        <v>15</v>
+      </c>
+      <c r="N83" t="s">
+        <v>146</v>
+      </c>
+      <c r="O83" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O83"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4886,54 +9194,54 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>96</v>
+        <v>241</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>101</v>
+        <v>245</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>102</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <v>25</v>
@@ -4948,27 +9256,27 @@
         <v>31000</v>
       </c>
       <c r="I2" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="J2">
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>250</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E3">
         <v>22400</v>
@@ -4983,30 +9291,30 @@
         <v>26842.5</v>
       </c>
       <c r="I3" t="s">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="J3">
         <v>215</v>
       </c>
       <c r="K3" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L3" t="s">
-        <v>111</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>254</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E4">
         <v>6700</v>
@@ -5021,30 +9329,30 @@
         <v>12442.5</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
       <c r="J4">
         <v>142</v>
       </c>
       <c r="K4" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L4" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>257</v>
       </c>
       <c r="E5">
         <v>5800</v>
@@ -5059,27 +9367,27 @@
         <v>9280</v>
       </c>
       <c r="I5" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>21600</v>
@@ -5094,30 +9402,30 @@
         <v>9259.039999999999</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="J6">
         <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L6" t="s">
-        <v>119</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>261</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <v>11800</v>
@@ -5132,30 +9440,30 @@
         <v>8443.68</v>
       </c>
       <c r="I7" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="J7">
         <v>75</v>
       </c>
       <c r="K7" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L7" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E8">
         <v>20100</v>
@@ -5170,30 +9478,30 @@
         <v>7863.52</v>
       </c>
       <c r="I8" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="J8">
         <v>23</v>
       </c>
       <c r="K8" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L8" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E9">
         <v>8500</v>
@@ -5208,30 +9516,30 @@
         <v>5582.08</v>
       </c>
       <c r="I9" t="s">
-        <v>127</v>
+        <v>267</v>
       </c>
       <c r="J9">
         <v>52</v>
       </c>
       <c r="K9" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L9" t="s">
-        <v>128</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>269</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>3200</v>
@@ -5246,30 +9554,30 @@
         <v>5332.5</v>
       </c>
       <c r="I10" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="J10">
         <v>66</v>
       </c>
       <c r="K10" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L10" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="E11">
         <v>8350</v>
@@ -5284,30 +9592,30 @@
         <v>1209</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>273</v>
       </c>
       <c r="J11">
         <v>151</v>
       </c>
       <c r="K11" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L11" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E12">
         <v>21900</v>
@@ -5322,30 +9630,30 @@
         <v>1106.6</v>
       </c>
       <c r="I12" t="s">
-        <v>137</v>
+        <v>276</v>
       </c>
       <c r="J12">
         <v>158</v>
       </c>
       <c r="K12" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L12" t="s">
-        <v>137</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="E13">
         <v>350</v>
@@ -5360,27 +9668,27 @@
         <v>1085</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>278</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>279</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="E14">
         <v>350</v>
@@ -5395,27 +9703,27 @@
         <v>1085</v>
       </c>
       <c r="I14" t="s">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="J14">
         <v>10</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="E15">
         <v>6900</v>
@@ -5430,30 +9738,30 @@
         <v>1035.4</v>
       </c>
       <c r="I15" t="s">
-        <v>143</v>
+        <v>282</v>
       </c>
       <c r="J15">
         <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L15" t="s">
-        <v>144</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>261</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="E16">
         <v>5300</v>
@@ -5468,30 +9776,30 @@
         <v>940.5</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="J16">
         <v>75</v>
       </c>
       <c r="K16" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L16" t="s">
-        <v>146</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>50</v>
@@ -5506,27 +9814,27 @@
         <v>910</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>285</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>18200</v>
@@ -5541,30 +9849,30 @@
         <v>773.64</v>
       </c>
       <c r="I18" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="J18">
         <v>87</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L18" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>288</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E19">
         <v>8350</v>
@@ -5579,27 +9887,27 @@
         <v>668</v>
       </c>
       <c r="I19" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="J19">
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>289</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>9500</v>
@@ -5614,30 +9922,30 @@
         <v>593.88</v>
       </c>
       <c r="I20" t="s">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="J20">
         <v>103</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L20" t="s">
-        <v>156</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>16900</v>
@@ -5652,30 +9960,30 @@
         <v>548.52</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>293</v>
       </c>
       <c r="J21">
         <v>198</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <v>8800</v>
@@ -5690,30 +9998,30 @@
         <v>409.7500000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>161</v>
+        <v>296</v>
       </c>
       <c r="J22">
         <v>117</v>
       </c>
       <c r="K22" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L22" t="s">
-        <v>162</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>298</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E23">
         <v>14900</v>
@@ -5728,30 +10036,30 @@
         <v>280.5</v>
       </c>
       <c r="I23" t="s">
-        <v>164</v>
+        <v>299</v>
       </c>
       <c r="J23">
         <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="E24">
         <v>14100</v>
@@ -5766,30 +10074,30 @@
         <v>232.06</v>
       </c>
       <c r="I24" t="s">
-        <v>167</v>
+        <v>301</v>
       </c>
       <c r="J24">
         <v>192</v>
       </c>
       <c r="K24" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L24" t="s">
-        <v>168</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>169</v>
+        <v>303</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E25">
         <v>2150</v>
@@ -5804,30 +10112,30 @@
         <v>225.6</v>
       </c>
       <c r="I25" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="J25">
         <v>205</v>
       </c>
       <c r="K25" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s">
-        <v>172</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E26">
         <v>2500</v>
@@ -5842,27 +10150,27 @@
         <v>200</v>
       </c>
       <c r="I26" t="s">
-        <v>143</v>
+        <v>282</v>
       </c>
       <c r="J26">
         <v>4</v>
       </c>
       <c r="K26" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E27">
         <v>1250</v>
@@ -5877,30 +10185,30 @@
         <v>117.6</v>
       </c>
       <c r="I27" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="J27">
         <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L27" t="s">
-        <v>176</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>310</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E28">
         <v>2400</v>
@@ -5915,30 +10223,30 @@
         <v>97.90000000000001</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="J28">
         <v>31</v>
       </c>
       <c r="K28" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s">
-        <v>179</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>7950</v>
@@ -5953,30 +10261,30 @@
         <v>84.04000000000001</v>
       </c>
       <c r="I29" t="s">
-        <v>182</v>
+        <v>314</v>
       </c>
       <c r="J29">
         <v>60</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L29" t="s">
-        <v>183</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>184</v>
+        <v>316</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="E30">
         <v>6350</v>
@@ -5991,30 +10299,30 @@
         <v>63.42000000000001</v>
       </c>
       <c r="I30" t="s">
-        <v>186</v>
+        <v>318</v>
       </c>
       <c r="J30">
         <v>122</v>
       </c>
       <c r="K30" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L30" t="s">
-        <v>187</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>320</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E31">
         <v>1100</v>
@@ -6029,30 +10337,30 @@
         <v>58.8</v>
       </c>
       <c r="I31" t="s">
-        <v>189</v>
+        <v>321</v>
       </c>
       <c r="J31">
         <v>212</v>
       </c>
       <c r="K31" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L31" t="s">
-        <v>190</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>323</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="E32">
         <v>6600</v>
@@ -6067,30 +10375,30 @@
         <v>56.28000000000001</v>
       </c>
       <c r="I32" t="s">
-        <v>167</v>
+        <v>301</v>
       </c>
       <c r="J32">
         <v>192</v>
       </c>
       <c r="K32" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L32" t="s">
-        <v>192</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="E33">
         <v>6950</v>
@@ -6105,30 +10413,30 @@
         <v>49.7</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
+        <v>326</v>
       </c>
       <c r="J33">
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L33" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>328</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="E34">
         <v>700</v>
@@ -6143,30 +10451,30 @@
         <v>33.48</v>
       </c>
       <c r="I34" t="s">
-        <v>198</v>
+        <v>329</v>
       </c>
       <c r="J34">
         <v>80</v>
       </c>
       <c r="K34" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L34" t="s">
-        <v>199</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>331</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="E35">
         <v>500</v>
@@ -6181,27 +10489,27 @@
         <v>30</v>
       </c>
       <c r="I35" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="J35">
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E36">
         <v>1200</v>
@@ -6216,30 +10524,30 @@
         <v>7.84</v>
       </c>
       <c r="I36" t="s">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="J36">
         <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L36" t="s">
-        <v>204</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="E37">
         <v>1760</v>
@@ -6254,30 +10562,30 @@
         <v>5.1</v>
       </c>
       <c r="I37" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="J37">
         <v>23</v>
       </c>
       <c r="K37" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s">
-        <v>206</v>
+        <v>336</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>337</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E38">
         <v>900</v>
@@ -6292,30 +10600,30 @@
         <v>4</v>
       </c>
       <c r="I38" t="s">
-        <v>208</v>
+        <v>338</v>
       </c>
       <c r="J38">
         <v>146</v>
       </c>
       <c r="K38" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L38" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E39">
         <v>550</v>
@@ -6330,30 +10638,30 @@
         <v>2.72</v>
       </c>
       <c r="I39" t="s">
-        <v>211</v>
+        <v>341</v>
       </c>
       <c r="J39">
         <v>188</v>
       </c>
       <c r="K39" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>213</v>
+        <v>343</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="E40">
         <v>200</v>
@@ -6368,30 +10676,30 @@
         <v>2.52</v>
       </c>
       <c r="I40" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="J40">
         <v>81</v>
       </c>
       <c r="K40" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L40" t="s">
-        <v>216</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="E41">
         <v>600</v>
@@ -6406,21 +10714,21 @@
         <v>1.86</v>
       </c>
       <c r="I41" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
       <c r="J41">
         <v>142</v>
       </c>
       <c r="K41" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="L41" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -6429,7 +10737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6448,51 +10756,51 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>222</v>
+        <v>351</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>226</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E2">
         <v>3.92</v>
@@ -6513,21 +10821,21 @@
         <v>819.2800000000026</v>
       </c>
       <c r="K2" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E3">
         <v>3.92</v>
@@ -6548,21 +10856,21 @@
         <v>376.3200000000012</v>
       </c>
       <c r="K3" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E4">
         <v>3.92</v>
@@ -6583,21 +10891,21 @@
         <v>90.16000000000028</v>
       </c>
       <c r="K4" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E5">
         <v>3.92</v>
@@ -6618,21 +10926,21 @@
         <v>525.2800000000017</v>
       </c>
       <c r="K5" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E6">
         <v>3.92</v>
@@ -6653,21 +10961,21 @@
         <v>493.9200000000016</v>
       </c>
       <c r="K6" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E7">
         <v>3.92</v>
@@ -6688,21 +10996,21 @@
         <v>729.1200000000023</v>
       </c>
       <c r="K7" t="s">
-        <v>199</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E8">
         <v>3.92</v>
@@ -6723,21 +11031,21 @@
         <v>180.3200000000006</v>
       </c>
       <c r="K8" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E9">
         <v>3.92</v>
@@ -6758,21 +11066,21 @@
         <v>1418.569600000005</v>
       </c>
       <c r="K9" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>368</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E10">
         <v>3.92</v>
@@ -6793,21 +11101,21 @@
         <v>1293.600000000004</v>
       </c>
       <c r="K10" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>3.92</v>
@@ -6828,21 +11136,21 @@
         <v>1277.920000000004</v>
       </c>
       <c r="K11" t="s">
-        <v>203</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>371</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E12">
         <v>3.92</v>
@@ -6863,7 +11171,7 @@
         <v>1160.320000000004</v>
       </c>
       <c r="K12" t="s">
-        <v>243</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -6871,7 +11179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6886,36 +11194,36 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>244</v>
+        <v>373</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>245</v>
+        <v>374</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>246</v>
+        <v>375</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>247</v>
+        <v>376</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>248</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>378</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -6927,21 +11235,21 @@
         <v>13300</v>
       </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="G2" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="H2" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -6953,21 +11261,21 @@
         <v>13900</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>382</v>
       </c>
       <c r="G3" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="H3" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -6979,21 +11287,21 @@
         <v>4600</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>278</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>278</v>
       </c>
       <c r="H4" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>385</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7005,21 +11313,21 @@
         <v>18300</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>255</v>
       </c>
       <c r="G5" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
       <c r="H5" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>371</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -7031,21 +11339,21 @@
         <v>14800</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="G6" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="H6" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7057,21 +11365,21 @@
         <v>15400</v>
       </c>
       <c r="F7" t="s">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="G7" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
       <c r="H7" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7083,21 +11391,21 @@
         <v>24700</v>
       </c>
       <c r="F8" t="s">
-        <v>263</v>
+        <v>392</v>
       </c>
       <c r="G8" t="s">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="H8" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>394</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7109,21 +11417,21 @@
         <v>15300</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>392</v>
       </c>
       <c r="G9" t="s">
-        <v>263</v>
+        <v>392</v>
       </c>
       <c r="H9" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7135,21 +11443,21 @@
         <v>23000</v>
       </c>
       <c r="F10" t="s">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>318</v>
       </c>
       <c r="H10" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>396</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -7161,21 +11469,21 @@
         <v>20000</v>
       </c>
       <c r="F11" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="H11" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>397</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7187,21 +11495,21 @@
         <v>9700</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="G12" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="H12" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -7213,21 +11521,21 @@
         <v>11800</v>
       </c>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="G13" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
       <c r="H13" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>271</v>
+        <v>400</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -7239,21 +11547,21 @@
         <v>2300</v>
       </c>
       <c r="F14" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="G14" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="H14" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>310</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -7265,21 +11573,21 @@
         <v>7200</v>
       </c>
       <c r="F15" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
       <c r="G15" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>402</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -7291,21 +11599,21 @@
         <v>11000</v>
       </c>
       <c r="F16" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
       <c r="G16" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
       <c r="H16" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>404</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -7317,21 +11625,21 @@
         <v>19800</v>
       </c>
       <c r="F17" t="s">
-        <v>276</v>
+        <v>405</v>
       </c>
       <c r="G17" t="s">
-        <v>276</v>
+        <v>405</v>
       </c>
       <c r="H17" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>406</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -7343,21 +11651,21 @@
         <v>11500</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="G18" t="s">
-        <v>278</v>
+        <v>407</v>
       </c>
       <c r="H18" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>408</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -7369,21 +11677,21 @@
         <v>3050</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="G19" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="H19" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>281</v>
+        <v>410</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -7395,21 +11703,21 @@
         <v>5900</v>
       </c>
       <c r="F20" t="s">
-        <v>282</v>
+        <v>411</v>
       </c>
       <c r="G20" t="s">
-        <v>182</v>
+        <v>314</v>
       </c>
       <c r="H20" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -7421,21 +11729,21 @@
         <v>1800</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>293</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>293</v>
       </c>
       <c r="H21" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>413</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -7447,21 +11755,21 @@
         <v>7200</v>
       </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="G22" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="H22" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>285</v>
+        <v>414</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -7473,21 +11781,21 @@
         <v>2000</v>
       </c>
       <c r="F23" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
       <c r="G23" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
       <c r="H23" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>415</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -7499,21 +11807,21 @@
         <v>7350</v>
       </c>
       <c r="F24" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="G24" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="H24" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>417</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -7525,21 +11833,21 @@
         <v>4600</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="G25" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="H25" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -7551,21 +11859,21 @@
         <v>5300</v>
       </c>
       <c r="F26" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="G26" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="H26" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -7577,21 +11885,21 @@
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="G27" t="s">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="H27" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -7603,21 +11911,21 @@
         <v>1320</v>
       </c>
       <c r="F28" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="G28" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="H28" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>294</v>
+        <v>423</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -7629,21 +11937,21 @@
         <v>720</v>
       </c>
       <c r="F29" t="s">
-        <v>295</v>
+        <v>424</v>
       </c>
       <c r="G29" t="s">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="H29" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -7655,21 +11963,21 @@
         <v>1800</v>
       </c>
       <c r="F30" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="G30" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="H30" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -7681,13 +11989,13 @@
         <v>1280</v>
       </c>
       <c r="F31" t="s">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="G31" t="s">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="H31" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -7695,7 +12003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7708,362 +12016,189 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>301</v>
+        <v>430</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>302</v>
+        <v>431</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>303</v>
+        <v>432</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>304</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>308</v>
+      <c r="A2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>310</v>
+      <c r="A3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>311</v>
+        <v>439</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>313</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>314</v>
+        <v>442</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>315</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>316</v>
+        <v>444</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>317</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>318</v>
+        <v>446</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>306</v>
+        <v>123</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>319</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>320</v>
+        <v>448</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>321</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>448</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>322</v>
+        <v>229</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>323</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>325</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>326</v>
+        <v>453</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>312</v>
+        <v>440</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="60.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="5">
-        <v>28187145.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>363</v>
-      </c>
-      <c r="B16" s="5">
-        <v>29503886.49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B17" s="5">
-        <v>25295562.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B18" s="5">
-        <v>75999.42763999989</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
